--- a/Listing/BAT01N.xlsx
+++ b/Listing/BAT01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="149">
   <si>
     <t/>
   </si>
@@ -175,10 +175,10 @@
     <t>ABC ALK AAA-LR03/2MP</t>
   </si>
   <si>
-    <t>10000610</t>
-  </si>
-  <si>
-    <t>ABC BATT. S/PWR 9V</t>
+    <t>20140180</t>
+  </si>
+  <si>
+    <t>ABC ALKALINE AA 8'S</t>
   </si>
   <si>
     <t>10025645</t>
@@ -187,15 +187,6 @@
     <t>ABC ALKALINE 9 VOLT</t>
   </si>
   <si>
-    <t>20111008</t>
-  </si>
-  <si>
-    <t>IDM MSKER 3PLY 5+2'S</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
     <t>20117862</t>
   </si>
   <si>
@@ -295,6 +286,9 @@
     <t>PKEMON KRT.SCAR SV1S</t>
   </si>
   <si>
+    <t>PT</t>
+  </si>
+  <si>
     <t>20129265</t>
   </si>
   <si>
@@ -317,9 +311,6 @@
   </si>
   <si>
     <t>POKEMON SET SPC SV5S</t>
-  </si>
-  <si>
-    <t>PT</t>
   </si>
   <si>
     <t>20134684</t>
@@ -859,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1407,15 +1398,15 @@
         <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1424,18 +1415,18 @@
         <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1447,15 +1438,15 @@
         <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1467,15 +1458,15 @@
         <v>8</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1487,15 +1478,15 @@
         <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1507,15 +1498,15 @@
         <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1524,18 +1515,18 @@
         <v>14</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1544,7 +1535,7 @@
         <v>14</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>63</v>
@@ -1552,10 +1543,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1564,7 +1555,7 @@
         <v>14</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>63</v>
@@ -1572,10 +1563,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1584,7 +1575,7 @@
         <v>14</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>63</v>
@@ -1592,10 +1583,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1604,7 +1595,7 @@
         <v>14</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>63</v>
@@ -1612,10 +1603,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -1624,7 +1615,7 @@
         <v>14</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>63</v>
@@ -1641,13 +1632,13 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1667,7 +1658,7 @@
         <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1687,7 +1678,7 @@
         <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1707,7 +1698,7 @@
         <v>4</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1727,7 +1718,7 @@
         <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1747,16 +1738,16 @@
         <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
@@ -1767,16 +1758,16 @@
         <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
@@ -1787,16 +1778,16 @@
         <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
@@ -1804,18 +1795,18 @@
         <v>17</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -1827,15 +1818,15 @@
         <v>8</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -1852,10 +1843,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -1867,16 +1858,16 @@
         <v>8</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
@@ -1884,15 +1875,18 @@
         <v>17</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -1904,15 +1898,15 @@
         <v>11</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -1924,15 +1918,15 @@
         <v>11</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -1944,16 +1938,16 @@
         <v>11</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>102</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
@@ -1961,18 +1955,18 @@
         <v>17</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -1984,15 +1978,15 @@
         <v>14</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2004,16 +1998,16 @@
         <v>14</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
@@ -2021,19 +2015,19 @@
         <v>17</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>102</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
@@ -2041,7 +2035,7 @@
         <v>17</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2049,22 +2043,22 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="E60" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2078,153 +2072,133 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
